--- a/Kế hoạch thực hiện.xlsx
+++ b/Kế hoạch thực hiện.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atif/Public/Final Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A0C0D2-BA8D-6443-90E3-67FD1EF1BBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9AB67C-BA71-8745-B97E-A84A1DE95831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kế hoạch chi tiết" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kế hoạch chi tiết'!$A$1:$K$104</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="513">
   <si>
     <t>STT</t>
   </si>
@@ -141,9 +141,6 @@
   </si>
   <si>
     <t>docs/03. Khảo sát/evidence/ + docs/03. Khảo sát/FIT_GAP.md</t>
-  </si>
-  <si>
-    <t>Đang làm</t>
   </si>
   <si>
     <t>QUY TẮC CỨNG #2: không nhận xét benchmark nếu chưa chạy thật. Bằng chứng đã lưu ở docs/03. Khảo sát/evidence/</t>
@@ -1687,7 +1684,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1730,12 +1727,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1858,7 +1849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1930,9 +1921,6 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1943,7 +1931,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2263,6 +2251,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{1DDB0475-30FB-1344-8874-DD3B5845D795}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;ca30ea4b-1450-4746-b6ea-b1fa5bd1e3c4&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K104"/>
@@ -2316,18 +2326,18 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="35"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20">
@@ -2358,7 +2368,7 @@
       <c r="J3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="27">
         <v>6</v>
       </c>
     </row>
@@ -2391,7 +2401,7 @@
       <c r="J4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="27">
         <v>6</v>
       </c>
     </row>
@@ -2424,7 +2434,7 @@
       <c r="J5" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="27">
         <v>8</v>
       </c>
     </row>
@@ -2457,7 +2467,7 @@
       <c r="J6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="27">
         <v>6</v>
       </c>
     </row>
@@ -2483,16 +2493,16 @@
       <c r="G7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="J7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="28">
+      <c r="K7" s="27">
         <v>6</v>
       </c>
     </row>
@@ -2504,30 +2514,30 @@
         <v>12</v>
       </c>
       <c r="C8" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="E8" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="F8" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="G8" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="28">
+      <c r="K8" s="27">
         <v>6</v>
       </c>
     </row>
@@ -2539,30 +2549,30 @@
         <v>12</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="23" t="s">
-        <v>45</v>
-      </c>
       <c r="F9" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="H9" s="20" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="28">
+      <c r="K9" s="27">
         <v>4</v>
       </c>
     </row>
@@ -2574,30 +2584,30 @@
         <v>12</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>49</v>
-      </c>
       <c r="F10" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="H10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="29">
+      <c r="K10" s="28">
         <v>3</v>
       </c>
     </row>
@@ -2609,79 +2619,79 @@
         <v>12</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>53</v>
-      </c>
       <c r="F11" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="H11" s="20" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="26" t="s">
+      <c r="K11" s="27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="34"/>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21">
         <v>10</v>
       </c>
       <c r="B13" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="D13" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="E13" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="F13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="G13" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="H13" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="I13" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="J13" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="29">
+      <c r="K13" s="28">
         <v>0</v>
       </c>
     </row>
@@ -2690,103 +2700,103 @@
         <v>11</v>
       </c>
       <c r="B14" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="F14" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="J14" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20">
+        <v>12</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21">
-        <v>12</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="J15" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="26" t="s">
+      <c r="K15" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20">
+        <v>13</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="K15" s="29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21">
-        <v>13</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="21" t="s">
+      <c r="D16" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="F16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="G16" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="H16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" s="24" t="s">
+      <c r="J16" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="K16" s="29">
+      <c r="K16" s="28">
         <v>6</v>
       </c>
     </row>
@@ -2795,33 +2805,33 @@
         <v>14</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="F17" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="24" t="s">
+      <c r="J17" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="J17" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="K17" s="29">
+      <c r="K17" s="28">
         <v>3</v>
       </c>
     </row>
@@ -2830,33 +2840,33 @@
         <v>15</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="F18" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I18" s="24" t="s">
+      <c r="J18" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="J18" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="K18" s="29">
+      <c r="K18" s="28">
         <v>3</v>
       </c>
     </row>
@@ -2865,82 +2875,82 @@
         <v>16</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="F19" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="24" t="s">
+      <c r="J19" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="J19" s="26" t="s">
+      <c r="K19" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="29">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34"/>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21">
         <v>17</v>
       </c>
       <c r="B21" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="D21" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="E21" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="F21" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="G21" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="H21" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="24" t="s">
+      <c r="J21" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="J21" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="K21" s="29">
+      <c r="K21" s="28">
         <v>8</v>
       </c>
     </row>
@@ -2949,33 +2959,33 @@
         <v>18</v>
       </c>
       <c r="B22" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>95</v>
-      </c>
       <c r="D22" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>103</v>
-      </c>
       <c r="F22" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="20" t="s">
         <v>98</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>99</v>
       </c>
       <c r="H22" s="20" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="J22" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="J22" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="K22" s="28">
+      <c r="K22" s="27">
         <v>10</v>
       </c>
     </row>
@@ -2984,33 +2994,33 @@
         <v>19</v>
       </c>
       <c r="B23" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>95</v>
-      </c>
       <c r="D23" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="23" t="s">
-        <v>107</v>
-      </c>
       <c r="F23" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="20" t="s">
         <v>98</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>99</v>
       </c>
       <c r="H23" s="20" t="s">
         <v>18</v>
       </c>
       <c r="I23" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="K23" s="28">
+      <c r="K23" s="27">
         <v>3</v>
       </c>
     </row>
@@ -3019,31 +3029,31 @@
         <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="E24" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="F24" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="G24" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="G24" s="21" t="s">
-        <v>114</v>
-      </c>
       <c r="H24" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I24" s="24"/>
       <c r="J24" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="K24" s="29">
+        <v>114</v>
+      </c>
+      <c r="K24" s="28">
         <v>8</v>
       </c>
     </row>
@@ -3052,31 +3062,31 @@
         <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D25" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="24" t="s">
-        <v>117</v>
-      </c>
       <c r="F25" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="G25" s="21" t="s">
-        <v>114</v>
-      </c>
       <c r="H25" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25" s="29">
+        <v>117</v>
+      </c>
+      <c r="K25" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3085,33 +3095,33 @@
         <v>22</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="F26" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="F26" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="24" t="s">
+      <c r="J26" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="J26" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="K26" s="29">
+      <c r="K26" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3120,33 +3130,33 @@
         <v>23</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="E27" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="31" t="s">
+      <c r="F27" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="G27" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="H27" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="H27" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>128</v>
-      </c>
       <c r="J27" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="29">
+        <v>64</v>
+      </c>
+      <c r="K27" s="28">
         <v>0</v>
       </c>
     </row>
@@ -3155,68 +3165,68 @@
         <v>24</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="F28" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="F28" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I28" s="24" t="s">
+      <c r="J28" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="J28" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="K28" s="29">
+      <c r="K28" s="28">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.2">
       <c r="A29" s="21">
         <v>97</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D29" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="F29" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I29" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I29" s="24" t="s">
+      <c r="J29" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="J29" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="K29" s="29">
+      <c r="K29" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3225,80 +3235,80 @@
         <v>25</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D30" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="F30" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J30" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J30" s="26" t="s">
+      <c r="K30" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="K30" s="29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="35"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="21">
         <v>26</v>
       </c>
       <c r="B32" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="D32" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="E32" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="F32" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="G32" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="G32" s="21" t="s">
-        <v>146</v>
-      </c>
       <c r="H32" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I32" s="24"/>
       <c r="J32" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="K32" s="29">
+        <v>146</v>
+      </c>
+      <c r="K32" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3307,31 +3317,31 @@
         <v>27</v>
       </c>
       <c r="B33" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>142</v>
-      </c>
       <c r="D33" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="24" t="s">
-        <v>149</v>
-      </c>
       <c r="F33" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="21" t="s">
-        <v>146</v>
-      </c>
       <c r="H33" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I33" s="24"/>
       <c r="J33" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="K33" s="29">
+        <v>149</v>
+      </c>
+      <c r="K33" s="28">
         <v>2</v>
       </c>
     </row>
@@ -3340,33 +3350,33 @@
         <v>28</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="21" t="s">
-        <v>142</v>
-      </c>
       <c r="D34" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E34" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="F34" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I34" s="24" t="s">
+      <c r="J34" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="J34" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="K34" s="29">
+      <c r="K34" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3375,31 +3385,31 @@
         <v>29</v>
       </c>
       <c r="B35" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>142</v>
-      </c>
       <c r="D35" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="E35" s="24" t="s">
-        <v>156</v>
-      </c>
       <c r="F35" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G35" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="G35" s="21" t="s">
-        <v>146</v>
-      </c>
       <c r="H35" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I35" s="24"/>
       <c r="J35" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="K35" s="29">
+        <v>156</v>
+      </c>
+      <c r="K35" s="28">
         <v>2</v>
       </c>
     </row>
@@ -3408,31 +3418,31 @@
         <v>30</v>
       </c>
       <c r="B36" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>142</v>
-      </c>
       <c r="D36" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="E36" s="24" t="s">
-        <v>159</v>
-      </c>
       <c r="F36" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="21" t="s">
-        <v>146</v>
-      </c>
       <c r="H36" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I36" s="24"/>
       <c r="J36" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="K36" s="29">
+        <v>159</v>
+      </c>
+      <c r="K36" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3441,33 +3451,33 @@
         <v>31</v>
       </c>
       <c r="B37" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="21" t="s">
-        <v>142</v>
-      </c>
       <c r="D37" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="F37" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="F37" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="H37" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I37" s="24" t="s">
+      <c r="J37" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="J37" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="K37" s="29">
+      <c r="K37" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3476,31 +3486,31 @@
         <v>32</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C38" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="E38" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="F38" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="G38" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="G38" s="21" t="s">
-        <v>169</v>
-      </c>
       <c r="H38" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I38" s="24"/>
       <c r="J38" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="K38" s="29">
+        <v>169</v>
+      </c>
+      <c r="K38" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3509,31 +3519,31 @@
         <v>33</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D39" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="E39" s="24" t="s">
-        <v>172</v>
-      </c>
       <c r="F39" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="G39" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="G39" s="21" t="s">
-        <v>169</v>
-      </c>
       <c r="H39" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I39" s="24"/>
       <c r="J39" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="K39" s="29">
+        <v>172</v>
+      </c>
+      <c r="K39" s="28">
         <v>2</v>
       </c>
     </row>
@@ -3542,31 +3552,31 @@
         <v>34</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D40" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="E40" s="24" t="s">
-        <v>175</v>
-      </c>
       <c r="F40" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="G40" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="G40" s="21" t="s">
-        <v>169</v>
-      </c>
       <c r="H40" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I40" s="24"/>
       <c r="J40" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="K40" s="29">
+        <v>175</v>
+      </c>
+      <c r="K40" s="28">
         <v>2</v>
       </c>
     </row>
@@ -3575,31 +3585,31 @@
         <v>35</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D41" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="E41" s="24" t="s">
-        <v>178</v>
-      </c>
       <c r="F41" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="G41" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="G41" s="21" t="s">
-        <v>169</v>
-      </c>
       <c r="H41" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I41" s="24"/>
       <c r="J41" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="K41" s="29">
+        <v>178</v>
+      </c>
+      <c r="K41" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3608,33 +3618,33 @@
         <v>36</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D42" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="F42" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I42" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="F42" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="G42" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="H42" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="24" t="s">
+      <c r="J42" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="J42" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="K42" s="29">
+      <c r="K42" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3643,33 +3653,33 @@
         <v>37</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D43" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="F43" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I43" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="F43" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="G43" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="H43" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I43" s="24" t="s">
+      <c r="J43" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="J43" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="K43" s="29">
+      <c r="K43" s="28">
         <v>2</v>
       </c>
     </row>
@@ -3678,33 +3688,33 @@
         <v>38</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C44" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="E44" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="E44" s="24" t="s">
+      <c r="F44" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F44" s="21" t="s">
+      <c r="G44" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="G44" s="21" t="s">
+      <c r="H44" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I44" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="H44" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I44" s="24" t="s">
+      <c r="J44" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="J44" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="K44" s="29">
+      <c r="K44" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3713,33 +3723,33 @@
         <v>39</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D45" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="F45" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I45" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="F45" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H45" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I45" s="24" t="s">
+      <c r="J45" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="J45" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="K45" s="29">
+      <c r="K45" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3748,33 +3758,33 @@
         <v>40</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D46" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="E46" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="E46" s="24" t="s">
+      <c r="F46" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I46" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="F46" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="G46" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H46" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I46" s="24" t="s">
+      <c r="J46" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="J46" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="K46" s="29">
+      <c r="K46" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3783,33 +3793,33 @@
         <v>41</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D47" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="F47" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I47" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="F47" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H47" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I47" s="24" t="s">
+      <c r="J47" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="J47" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="K47" s="29">
+      <c r="K47" s="28">
         <v>2</v>
       </c>
     </row>
@@ -3818,31 +3828,31 @@
         <v>42</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D48" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="E48" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="E48" s="24" t="s">
-        <v>208</v>
-      </c>
       <c r="F48" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G48" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="G48" s="21" t="s">
-        <v>192</v>
-      </c>
       <c r="H48" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I48" s="24"/>
       <c r="J48" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="K48" s="29">
+        <v>208</v>
+      </c>
+      <c r="K48" s="28">
         <v>2</v>
       </c>
     </row>
@@ -3851,31 +3861,31 @@
         <v>43</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D49" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="E49" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="F49" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G49" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="G49" s="21" t="s">
-        <v>192</v>
-      </c>
       <c r="H49" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I49" s="24"/>
       <c r="J49" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="K49" s="29">
+        <v>211</v>
+      </c>
+      <c r="K49" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3884,33 +3894,33 @@
         <v>44</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D50" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="F50" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I50" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="F50" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H50" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I50" s="24" t="s">
+      <c r="J50" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="J50" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="K50" s="29">
+      <c r="K50" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3919,31 +3929,31 @@
         <v>45</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D51" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E51" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="E51" s="24" t="s">
-        <v>218</v>
-      </c>
       <c r="F51" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G51" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="G51" s="21" t="s">
-        <v>192</v>
-      </c>
       <c r="H51" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I51" s="24"/>
       <c r="J51" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="K51" s="29">
+        <v>218</v>
+      </c>
+      <c r="K51" s="28">
         <v>3</v>
       </c>
     </row>
@@ -3952,33 +3962,33 @@
         <v>46</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D52" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="E52" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="F52" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="H52" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I52" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="F52" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H52" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I52" s="24" t="s">
+      <c r="J52" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="J52" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="K52" s="29">
+      <c r="K52" s="28">
         <v>4</v>
       </c>
     </row>
@@ -3987,33 +3997,33 @@
         <v>47</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C53" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="D53" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="D53" s="24" t="s">
+      <c r="E53" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="F53" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="G53" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="G53" s="21" t="s">
+      <c r="H53" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I53" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="H53" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I53" s="24" t="s">
+      <c r="J53" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="J53" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="K53" s="29">
+      <c r="K53" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4022,33 +4032,33 @@
         <v>48</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D54" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="E54" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="F54" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H54" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I54" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="F54" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G54" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H54" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I54" s="24" t="s">
+      <c r="J54" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="J54" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="K54" s="29">
+      <c r="K54" s="28">
         <v>5</v>
       </c>
     </row>
@@ -4057,33 +4067,33 @@
         <v>49</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D55" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="E55" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="F55" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I55" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="F55" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G55" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H55" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I55" s="24" t="s">
+      <c r="J55" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="J55" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="K55" s="29">
+      <c r="K55" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4092,33 +4102,33 @@
         <v>50</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D56" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="E56" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="F56" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H56" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I56" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="F56" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G56" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H56" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I56" s="24" t="s">
+      <c r="J56" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="J56" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="K56" s="29">
+      <c r="K56" s="28">
         <v>5</v>
       </c>
     </row>
@@ -4127,33 +4137,33 @@
         <v>51</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D57" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E57" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="F57" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I57" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="F57" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G57" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H57" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I57" s="24" t="s">
+      <c r="J57" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="J57" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="K57" s="29">
+      <c r="K57" s="28">
         <v>3</v>
       </c>
     </row>
@@ -4162,33 +4172,33 @@
         <v>52</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D58" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E58" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="F58" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I58" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="F58" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G58" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H58" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I58" s="24" t="s">
+      <c r="J58" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="J58" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="K58" s="29">
+      <c r="K58" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4197,33 +4207,33 @@
         <v>53</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D59" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="E59" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="E59" s="24" t="s">
+      <c r="F59" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H59" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I59" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="F59" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G59" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H59" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I59" s="24" t="s">
+      <c r="J59" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="J59" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="K59" s="29">
+      <c r="K59" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4232,31 +4242,31 @@
         <v>54</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D60" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E60" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="E60" s="24" t="s">
-        <v>256</v>
-      </c>
       <c r="F60" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G60" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="G60" s="21" t="s">
-        <v>228</v>
-      </c>
       <c r="H60" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I60" s="24"/>
       <c r="J60" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="K60" s="29">
+        <v>256</v>
+      </c>
+      <c r="K60" s="28">
         <v>2</v>
       </c>
     </row>
@@ -4265,31 +4275,31 @@
         <v>55</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D61" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="E61" s="24" t="s">
         <v>258</v>
       </c>
-      <c r="E61" s="24" t="s">
-        <v>259</v>
-      </c>
       <c r="F61" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G61" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="G61" s="21" t="s">
-        <v>228</v>
-      </c>
       <c r="H61" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I61" s="24"/>
       <c r="J61" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="K61" s="29">
+        <v>259</v>
+      </c>
+      <c r="K61" s="28">
         <v>2</v>
       </c>
     </row>
@@ -4298,33 +4308,33 @@
         <v>56</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D62" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="E62" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="F62" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G62" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H62" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I62" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="F62" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H62" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I62" s="24" t="s">
+      <c r="J62" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="J62" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="K62" s="29">
+      <c r="K62" s="28">
         <v>3</v>
       </c>
     </row>
@@ -4333,33 +4343,33 @@
         <v>57</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D63" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="E63" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="F63" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G63" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H63" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I63" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="F63" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G63" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I63" s="24" t="s">
+      <c r="J63" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="J63" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="K63" s="29">
+      <c r="K63" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4368,33 +4378,33 @@
         <v>58</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D64" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="E64" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="E64" s="24" t="s">
+      <c r="F64" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G64" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I64" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="F64" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G64" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H64" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I64" s="24" t="s">
+      <c r="J64" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="J64" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="K64" s="29">
+      <c r="K64" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4403,80 +4413,80 @@
         <v>59</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D65" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="E65" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="F65" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I65" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J65" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="F65" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="G65" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="H65" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J65" s="26" t="s">
+      <c r="K65" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="K65" s="29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="B66" s="34"/>
-      <c r="C66" s="34"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="34"/>
-      <c r="I66" s="34"/>
-      <c r="J66" s="35"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="33"/>
+      <c r="J66" s="34"/>
     </row>
     <row r="67" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="21">
         <v>60</v>
       </c>
       <c r="B67" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C67" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="D67" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="E67" s="24" t="s">
         <v>279</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="F67" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="F67" s="21" t="s">
+      <c r="G67" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="G67" s="21" t="s">
-        <v>282</v>
-      </c>
       <c r="H67" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I67" s="24"/>
       <c r="J67" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="K67" s="29">
+        <v>282</v>
+      </c>
+      <c r="K67" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4485,33 +4495,33 @@
         <v>61</v>
       </c>
       <c r="B68" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C68" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C68" s="21" t="s">
-        <v>278</v>
-      </c>
       <c r="D68" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="E68" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="F68" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="G68" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="H68" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I68" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="F68" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G68" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="H68" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I68" s="24" t="s">
+      <c r="J68" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="J68" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="K68" s="29">
+      <c r="K68" s="28">
         <v>5</v>
       </c>
     </row>
@@ -4520,33 +4530,33 @@
         <v>62</v>
       </c>
       <c r="B69" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C69" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C69" s="21" t="s">
-        <v>278</v>
-      </c>
       <c r="D69" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="E69" s="24" t="s">
         <v>288</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="F69" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="G69" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="H69" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I69" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="F69" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G69" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I69" s="24" t="s">
+      <c r="J69" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="J69" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="K69" s="29">
+      <c r="K69" s="28">
         <v>3</v>
       </c>
     </row>
@@ -4555,31 +4565,31 @@
         <v>63</v>
       </c>
       <c r="B70" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C70" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C70" s="21" t="s">
-        <v>278</v>
-      </c>
       <c r="D70" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="E70" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E70" s="24" t="s">
-        <v>293</v>
-      </c>
       <c r="F70" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="G70" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="G70" s="21" t="s">
-        <v>282</v>
-      </c>
       <c r="H70" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I70" s="24"/>
       <c r="J70" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="K70" s="29">
+        <v>293</v>
+      </c>
+      <c r="K70" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4588,33 +4598,33 @@
         <v>64</v>
       </c>
       <c r="B71" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C71" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C71" s="21" t="s">
-        <v>278</v>
-      </c>
       <c r="D71" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="E71" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="E71" s="24" t="s">
+      <c r="F71" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="H71" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I71" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="F71" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G71" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="H71" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I71" s="24" t="s">
+      <c r="J71" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="J71" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="K71" s="29">
+      <c r="K71" s="28">
         <v>3</v>
       </c>
     </row>
@@ -4623,31 +4633,31 @@
         <v>65</v>
       </c>
       <c r="B72" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C72" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C72" s="21" t="s">
-        <v>278</v>
-      </c>
       <c r="D72" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="E72" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="E72" s="24" t="s">
-        <v>300</v>
-      </c>
       <c r="F72" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="G72" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="G72" s="21" t="s">
-        <v>282</v>
-      </c>
       <c r="H72" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I72" s="24"/>
       <c r="J72" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="K72" s="29">
+        <v>300</v>
+      </c>
+      <c r="K72" s="28">
         <v>2</v>
       </c>
     </row>
@@ -4656,33 +4666,33 @@
         <v>66</v>
       </c>
       <c r="B73" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C73" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C73" s="21" t="s">
-        <v>278</v>
-      </c>
       <c r="D73" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="E73" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="F73" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="H73" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I73" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="F73" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G73" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="H73" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I73" s="24" t="s">
+      <c r="J73" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="J73" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="K73" s="29">
+      <c r="K73" s="28">
         <v>2</v>
       </c>
     </row>
@@ -4691,31 +4701,31 @@
         <v>67</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C74" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D74" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="E74" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="E74" s="24" t="s">
+      <c r="F74" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="F74" s="21" t="s">
+      <c r="G74" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G74" s="21" t="s">
-        <v>310</v>
-      </c>
       <c r="H74" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I74" s="24"/>
       <c r="J74" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="K74" s="29">
+        <v>310</v>
+      </c>
+      <c r="K74" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4724,31 +4734,31 @@
         <v>68</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D75" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E75" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="E75" s="24" t="s">
-        <v>313</v>
-      </c>
       <c r="F75" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="G75" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G75" s="21" t="s">
-        <v>310</v>
-      </c>
       <c r="H75" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I75" s="24"/>
       <c r="J75" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="K75" s="29">
+        <v>313</v>
+      </c>
+      <c r="K75" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4757,33 +4767,33 @@
         <v>69</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D76" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="D76" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="E76" s="30" t="s">
         <v>315</v>
       </c>
-      <c r="E76" s="31" t="s">
+      <c r="F76" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="H76" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="I76" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="F76" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G76" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="H76" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="I76" s="24" t="s">
-        <v>317</v>
-      </c>
       <c r="J76" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="K76" s="29">
+        <v>64</v>
+      </c>
+      <c r="K76" s="28">
         <v>0</v>
       </c>
     </row>
@@ -4792,33 +4802,33 @@
         <v>70</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D77" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="E77" s="24" t="s">
         <v>318</v>
       </c>
-      <c r="E77" s="24" t="s">
+      <c r="F77" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I77" s="24" t="s">
         <v>319</v>
       </c>
-      <c r="F77" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="H77" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I77" s="24" t="s">
+      <c r="J77" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="J77" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="K77" s="29">
+      <c r="K77" s="28">
         <v>5</v>
       </c>
     </row>
@@ -4827,33 +4837,33 @@
         <v>71</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D78" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="E78" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="E78" s="24" t="s">
+      <c r="F78" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="H78" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I78" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="F78" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="H78" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I78" s="24" t="s">
+      <c r="J78" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="J78" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="K78" s="29">
+      <c r="K78" s="28">
         <v>3</v>
       </c>
     </row>
@@ -4862,33 +4872,33 @@
         <v>72</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D79" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="E79" s="24" t="s">
         <v>326</v>
       </c>
-      <c r="E79" s="24" t="s">
+      <c r="F79" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="H79" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I79" s="24" t="s">
         <v>327</v>
       </c>
-      <c r="F79" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="H79" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I79" s="24" t="s">
+      <c r="J79" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="J79" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="K79" s="29">
+      <c r="K79" s="28">
         <v>3</v>
       </c>
     </row>
@@ -4897,33 +4907,33 @@
         <v>73</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C80" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D80" s="24" t="s">
         <v>330</v>
       </c>
-      <c r="D80" s="24" t="s">
+      <c r="E80" s="24" t="s">
         <v>331</v>
       </c>
-      <c r="E80" s="24" t="s">
+      <c r="F80" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="F80" s="21" t="s">
+      <c r="G80" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="G80" s="21" t="s">
+      <c r="H80" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I80" s="24" t="s">
         <v>334</v>
       </c>
-      <c r="H80" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I80" s="24" t="s">
+      <c r="J80" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="J80" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="K80" s="29">
+      <c r="K80" s="28">
         <v>4</v>
       </c>
     </row>
@@ -4932,33 +4942,33 @@
         <v>74</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D81" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="E81" s="24" t="s">
         <v>337</v>
       </c>
-      <c r="E81" s="24" t="s">
+      <c r="F81" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I81" s="24" t="s">
         <v>338</v>
       </c>
-      <c r="F81" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="G81" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="H81" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I81" s="24" t="s">
+      <c r="J81" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="J81" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="K81" s="29">
+      <c r="K81" s="28">
         <v>5</v>
       </c>
     </row>
@@ -4967,33 +4977,33 @@
         <v>75</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D82" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="E82" s="24" t="s">
         <v>341</v>
       </c>
-      <c r="E82" s="24" t="s">
+      <c r="F82" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="G82" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I82" s="24" t="s">
         <v>342</v>
       </c>
-      <c r="F82" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="G82" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="H82" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I82" s="24" t="s">
+      <c r="J82" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="J82" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="K82" s="29">
+      <c r="K82" s="28">
         <v>4</v>
       </c>
     </row>
@@ -5002,33 +5012,33 @@
         <v>76</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D83" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="E83" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="E83" s="24" t="s">
+      <c r="F83" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I83" s="24" t="s">
         <v>346</v>
       </c>
-      <c r="F83" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="G83" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="H83" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I83" s="24" t="s">
+      <c r="J83" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="J83" s="26" t="s">
-        <v>348</v>
-      </c>
-      <c r="K83" s="29">
+      <c r="K83" s="28">
         <v>3</v>
       </c>
     </row>
@@ -5037,82 +5047,82 @@
         <v>77</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D84" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="E84" s="24" t="s">
         <v>349</v>
       </c>
-      <c r="E84" s="24" t="s">
+      <c r="F84" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="G84" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="H84" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I84" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J84" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="F84" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="G84" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="H84" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I84" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J84" s="26" t="s">
+      <c r="K84" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="32" t="s">
         <v>351</v>
       </c>
-      <c r="K84" s="29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="B85" s="34"/>
-      <c r="C85" s="34"/>
-      <c r="D85" s="34"/>
-      <c r="E85" s="34"/>
-      <c r="F85" s="34"/>
-      <c r="G85" s="34"/>
-      <c r="H85" s="34"/>
-      <c r="I85" s="34"/>
-      <c r="J85" s="35"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="33"/>
+      <c r="D85" s="33"/>
+      <c r="E85" s="33"/>
+      <c r="F85" s="33"/>
+      <c r="G85" s="33"/>
+      <c r="H85" s="33"/>
+      <c r="I85" s="33"/>
+      <c r="J85" s="34"/>
     </row>
     <row r="86" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="21">
         <v>78</v>
       </c>
       <c r="B86" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C86" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C86" s="21" t="s">
+      <c r="D86" s="24" t="s">
         <v>354</v>
       </c>
-      <c r="D86" s="24" t="s">
+      <c r="E86" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="E86" s="24" t="s">
+      <c r="F86" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="F86" s="21" t="s">
+      <c r="G86" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="G86" s="21" t="s">
+      <c r="H86" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I86" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="H86" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I86" s="24" t="s">
+      <c r="J86" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="J86" s="26" t="s">
-        <v>360</v>
-      </c>
-      <c r="K86" s="29">
+      <c r="K86" s="28">
         <v>4</v>
       </c>
     </row>
@@ -5121,33 +5131,33 @@
         <v>79</v>
       </c>
       <c r="B87" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C87" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C87" s="21" t="s">
-        <v>354</v>
-      </c>
       <c r="D87" s="24" t="s">
+        <v>360</v>
+      </c>
+      <c r="E87" s="24" t="s">
         <v>361</v>
       </c>
-      <c r="E87" s="24" t="s">
+      <c r="F87" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="G87" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="H87" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I87" s="24" t="s">
         <v>362</v>
       </c>
-      <c r="F87" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="G87" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="H87" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I87" s="24" t="s">
+      <c r="J87" s="26" t="s">
         <v>363</v>
       </c>
-      <c r="J87" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="K87" s="29">
+      <c r="K87" s="28">
         <v>10</v>
       </c>
     </row>
@@ -5156,33 +5166,33 @@
         <v>80</v>
       </c>
       <c r="B88" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C88" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C88" s="21" t="s">
-        <v>354</v>
-      </c>
       <c r="D88" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E88" s="24" t="s">
         <v>365</v>
       </c>
-      <c r="E88" s="24" t="s">
+      <c r="F88" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="G88" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="H88" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I88" s="24" t="s">
         <v>366</v>
       </c>
-      <c r="F88" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="G88" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="H88" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I88" s="24" t="s">
+      <c r="J88" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="J88" s="26" t="s">
-        <v>368</v>
-      </c>
-      <c r="K88" s="29">
+      <c r="K88" s="28">
         <v>7</v>
       </c>
     </row>
@@ -5191,33 +5201,33 @@
         <v>81</v>
       </c>
       <c r="B89" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C89" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C89" s="21" t="s">
-        <v>354</v>
-      </c>
       <c r="D89" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="E89" s="24" t="s">
         <v>369</v>
       </c>
-      <c r="E89" s="24" t="s">
+      <c r="F89" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="G89" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="H89" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I89" s="24" t="s">
         <v>370</v>
       </c>
-      <c r="F89" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="G89" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="H89" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I89" s="24" t="s">
+      <c r="J89" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="J89" s="26" t="s">
-        <v>372</v>
-      </c>
-      <c r="K89" s="29">
+      <c r="K89" s="28">
         <v>5</v>
       </c>
     </row>
@@ -5226,33 +5236,33 @@
         <v>82</v>
       </c>
       <c r="B90" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C90" s="21" t="s">
-        <v>354</v>
-      </c>
       <c r="D90" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="E90" s="24" t="s">
         <v>373</v>
       </c>
-      <c r="E90" s="24" t="s">
+      <c r="F90" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="G90" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="H90" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I90" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="F90" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="G90" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="H90" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I90" s="24" t="s">
+      <c r="J90" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="J90" s="26" t="s">
-        <v>376</v>
-      </c>
-      <c r="K90" s="29">
+      <c r="K90" s="28">
         <v>4</v>
       </c>
     </row>
@@ -5261,33 +5271,33 @@
         <v>83</v>
       </c>
       <c r="B91" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C91" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C91" s="21" t="s">
-        <v>354</v>
-      </c>
       <c r="D91" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="E91" s="24" t="s">
         <v>377</v>
       </c>
-      <c r="E91" s="24" t="s">
+      <c r="F91" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="G91" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="H91" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I91" s="24" t="s">
         <v>378</v>
       </c>
-      <c r="F91" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="G91" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="H91" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I91" s="24" t="s">
+      <c r="J91" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="J91" s="26" t="s">
-        <v>380</v>
-      </c>
-      <c r="K91" s="29">
+      <c r="K91" s="28">
         <v>5</v>
       </c>
     </row>
@@ -5296,33 +5306,33 @@
         <v>84</v>
       </c>
       <c r="B92" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C92" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C92" s="21" t="s">
-        <v>354</v>
-      </c>
       <c r="D92" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="E92" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="E92" s="24" t="s">
+      <c r="F92" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="G92" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="H92" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I92" s="24" t="s">
         <v>382</v>
       </c>
-      <c r="F92" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="G92" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="H92" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I92" s="24" t="s">
+      <c r="J92" s="26" t="s">
         <v>383</v>
       </c>
-      <c r="J92" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="K92" s="29">
+      <c r="K92" s="28">
         <v>5</v>
       </c>
     </row>
@@ -5331,33 +5341,33 @@
         <v>85</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C93" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="D93" s="24" t="s">
         <v>385</v>
       </c>
-      <c r="D93" s="24" t="s">
+      <c r="E93" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="E93" s="24" t="s">
+      <c r="F93" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="F93" s="21" t="s">
+      <c r="G93" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="G93" s="21" t="s">
+      <c r="H93" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I93" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="H93" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I93" s="24" t="s">
+      <c r="J93" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="J93" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="K93" s="29">
+      <c r="K93" s="28">
         <v>4</v>
       </c>
     </row>
@@ -5366,33 +5376,33 @@
         <v>86</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D94" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="E94" s="24" t="s">
         <v>392</v>
       </c>
-      <c r="E94" s="24" t="s">
+      <c r="F94" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G94" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H94" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I94" s="24" t="s">
         <v>393</v>
       </c>
-      <c r="F94" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G94" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="H94" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I94" s="24" t="s">
+      <c r="J94" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="J94" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="K94" s="29">
+      <c r="K94" s="28">
         <v>3</v>
       </c>
     </row>
@@ -5401,31 +5411,31 @@
         <v>87</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D95" s="24" t="s">
+        <v>395</v>
+      </c>
+      <c r="E95" s="24" t="s">
         <v>396</v>
       </c>
-      <c r="E95" s="24" t="s">
-        <v>397</v>
-      </c>
       <c r="F95" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G95" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="G95" s="21" t="s">
-        <v>389</v>
-      </c>
       <c r="H95" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I95" s="24"/>
       <c r="J95" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="K95" s="29">
+        <v>397</v>
+      </c>
+      <c r="K95" s="28">
         <v>4</v>
       </c>
     </row>
@@ -5434,31 +5444,31 @@
         <v>88</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D96" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="E96" s="24" t="s">
         <v>399</v>
       </c>
-      <c r="E96" s="24" t="s">
-        <v>400</v>
-      </c>
       <c r="F96" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G96" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="G96" s="21" t="s">
-        <v>389</v>
-      </c>
       <c r="H96" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I96" s="24"/>
       <c r="J96" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="K96" s="29">
+        <v>400</v>
+      </c>
+      <c r="K96" s="28">
         <v>6</v>
       </c>
     </row>
@@ -5467,33 +5477,33 @@
         <v>89</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="D97" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="D97" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="E97" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="E97" s="31" t="s">
+      <c r="F97" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G97" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H97" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="I97" s="24" t="s">
         <v>403</v>
       </c>
-      <c r="F97" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G97" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="H97" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="I97" s="24" t="s">
-        <v>404</v>
-      </c>
       <c r="J97" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="K97" s="29">
+        <v>64</v>
+      </c>
+      <c r="K97" s="28">
         <v>0</v>
       </c>
     </row>
@@ -5502,33 +5512,33 @@
         <v>90</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D98" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="E98" s="24" t="s">
         <v>405</v>
       </c>
-      <c r="E98" s="24" t="s">
+      <c r="F98" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G98" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H98" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I98" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="F98" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G98" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="H98" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I98" s="24" t="s">
+      <c r="J98" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="J98" s="26" t="s">
-        <v>408</v>
-      </c>
-      <c r="K98" s="29">
+      <c r="K98" s="28">
         <v>6</v>
       </c>
     </row>
@@ -5537,33 +5547,33 @@
         <v>91</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D99" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E99" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="E99" s="24" t="s">
+      <c r="F99" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G99" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H99" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I99" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="F99" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G99" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="H99" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I99" s="24" t="s">
+      <c r="J99" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="J99" s="26" t="s">
-        <v>412</v>
-      </c>
-      <c r="K99" s="29">
+      <c r="K99" s="28">
         <v>3</v>
       </c>
     </row>
@@ -5572,31 +5582,31 @@
         <v>92</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D100" s="24" t="s">
+        <v>412</v>
+      </c>
+      <c r="E100" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="E100" s="24" t="s">
-        <v>414</v>
-      </c>
       <c r="F100" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G100" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="G100" s="21" t="s">
-        <v>389</v>
-      </c>
       <c r="H100" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I100" s="24"/>
       <c r="J100" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="K100" s="29">
+        <v>414</v>
+      </c>
+      <c r="K100" s="28">
         <v>3</v>
       </c>
     </row>
@@ -5605,33 +5615,33 @@
         <v>93</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D101" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="E101" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="E101" s="24" t="s">
+      <c r="F101" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G101" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H101" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I101" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="F101" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G101" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="H101" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I101" s="24" t="s">
+      <c r="J101" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="J101" s="26" t="s">
-        <v>419</v>
-      </c>
-      <c r="K101" s="29">
+      <c r="K101" s="28">
         <v>4</v>
       </c>
     </row>
@@ -5640,31 +5650,31 @@
         <v>94</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D102" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="E102" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="E102" s="24" t="s">
-        <v>421</v>
-      </c>
       <c r="F102" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G102" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="G102" s="21" t="s">
-        <v>389</v>
-      </c>
       <c r="H102" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I102" s="24"/>
       <c r="J102" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="K102" s="29">
+        <v>421</v>
+      </c>
+      <c r="K102" s="28">
         <v>5</v>
       </c>
     </row>
@@ -5673,33 +5683,33 @@
         <v>95</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D103" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="E103" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="F103" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G103" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H103" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I103" s="24" t="s">
         <v>423</v>
       </c>
-      <c r="E103" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="F103" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G103" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="H103" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I103" s="24" t="s">
+      <c r="J103" s="26" t="s">
         <v>424</v>
       </c>
-      <c r="J103" s="26" t="s">
-        <v>425</v>
-      </c>
-      <c r="K103" s="29">
+      <c r="K103" s="28">
         <v>3</v>
       </c>
     </row>
@@ -5708,33 +5718,33 @@
         <v>96</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D104" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="E104" s="24" t="s">
         <v>426</v>
       </c>
-      <c r="E104" s="24" t="s">
+      <c r="F104" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G104" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="H104" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I104" s="24" t="s">
         <v>427</v>
       </c>
-      <c r="F104" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G104" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="H104" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="I104" s="24" t="s">
+      <c r="J104" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="J104" s="26" t="s">
-        <v>429</v>
-      </c>
-      <c r="K104" s="29">
+      <c r="K104" s="28">
         <v>6</v>
       </c>
     </row>
@@ -5767,242 +5777,242 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>433</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" t="s">
         <v>437</v>
       </c>
-      <c r="E2" t="s">
-        <v>438</v>
-      </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E3" t="s">
         <v>440</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E3" t="s">
-        <v>441</v>
-      </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" t="s">
         <v>444</v>
       </c>
-      <c r="E4" t="s">
-        <v>445</v>
-      </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" t="s">
         <v>448</v>
       </c>
-      <c r="E5" t="s">
-        <v>449</v>
-      </c>
       <c r="F5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" t="s">
         <v>452</v>
       </c>
-      <c r="E6" t="s">
-        <v>453</v>
-      </c>
       <c r="F6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>453</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" t="s">
         <v>456</v>
       </c>
-      <c r="E7" t="s">
-        <v>457</v>
-      </c>
       <c r="F7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" t="s">
         <v>460</v>
       </c>
-      <c r="E8" t="s">
-        <v>461</v>
-      </c>
       <c r="F8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>461</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" t="s">
         <v>464</v>
       </c>
-      <c r="E9" t="s">
-        <v>465</v>
-      </c>
       <c r="F9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>465</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" t="s">
         <v>468</v>
       </c>
-      <c r="E10" t="s">
-        <v>469</v>
-      </c>
       <c r="F10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>469</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>472</v>
-      </c>
       <c r="E11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>472</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" t="s">
         <v>475</v>
       </c>
-      <c r="E12" t="s">
-        <v>476</v>
-      </c>
       <c r="F12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -6039,19 +6049,19 @@
         <v>2</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>477</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>480</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -6059,7 +6069,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -6083,10 +6093,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -6110,10 +6120,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -6137,10 +6147,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -6164,10 +6174,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -6191,10 +6201,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -6217,77 +6227,77 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="30" t="s">
-        <v>488</v>
-      </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30">
+      <c r="A8" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29">
         <f>SUM(C2:C7)</f>
         <v>17</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <f>SUM(D2:D7)</f>
         <v>340</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <f>SUM(E2:E7)</f>
         <v>392</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <f>SUM(F2:F7)</f>
         <v>-52</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="29">
         <f>SUM(G2:G7)</f>
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="30" t="s">
-        <v>489</v>
+      <c r="A10" s="29" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B11">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="29" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="36" t="s">
-        <v>491</v>
-      </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
+      <c r="A14" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6313,12 +6323,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B2" s="16"/>
       <c r="D2" s="6"/>
@@ -6326,13 +6336,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B3" s="10">
         <v>46272</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D3" s="10">
         <v>46285</v>
@@ -6342,13 +6352,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B4" s="10">
         <v>46286</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D4" s="10">
         <v>46299</v>
@@ -6357,16 +6367,16 @@
       <c r="F4" s="9"/>
     </row>
     <row r="6" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
-        <v>497</v>
-      </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
+      <c r="A6" s="41" t="s">
+        <v>496</v>
+      </c>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
     </row>
     <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -6376,7 +6386,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>5</v>
@@ -6385,13 +6395,13 @@
         <v>6</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6399,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="13"/>
@@ -6413,7 +6423,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="13"/>
@@ -6459,16 +6469,16 @@
       <c r="H12" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="42" t="s">
-        <v>503</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
+      <c r="A14" s="41" t="s">
+        <v>502</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
     </row>
     <row r="15" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
@@ -6478,7 +6488,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>5</v>
@@ -6487,13 +6497,13 @@
         <v>6</v>
       </c>
       <c r="F15" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>506</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6557,37 +6567,37 @@
       <c r="H20" s="12"/>
     </row>
     <row r="22" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="42" t="s">
-        <v>508</v>
-      </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
+      <c r="A22" s="41" t="s">
+        <v>507</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
     </row>
     <row r="23" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="37" t="s">
         <v>510</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="E23" s="39"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="7" t="s">
+      <c r="H23" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -6596,9 +6606,9 @@
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
     </row>
@@ -6608,9 +6618,9 @@
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="12"/>
       <c r="H25" s="13"/>
     </row>
@@ -6620,9 +6630,9 @@
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="12"/>
       <c r="H26" s="13"/>
     </row>

--- a/Kế hoạch thực hiện.xlsx
+++ b/Kế hoạch thực hiện.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Kế hoạch chi tiết" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tổng quan mốc" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Khối lượng giờ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Báo cáo 2 tuần" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kế hoạch chi tiết" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng quan mốc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối lượng giờ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Báo cáo 2 tuần" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kế hoạch chi tiết'!$A$1:$K$104</definedName>
@@ -1503,49 +1503,15 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="36">
-      <c r="A17" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>ND2</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>Tuần 5</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>Chốt tên chính xác 3 model đích: A1 frontier / A2 lớp doanh nghiệp Việt / A3 lớp rẻ. Thêm khối targets vào config/models.yaml + .env, KHÔNG sửa code</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>config/models.yaml + .env</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>11/10/2026</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>Xong</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>Xong thì git tag v-models-1.0. Không đổi model sau mốc này</t>
-        </is>
-      </c>
+      <c r="A17" s="20" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="23" t="n"/>
       <c r="J17" s="26" t="inlineStr">
         <is>
           <t>Claude soạn khối targets trong models.yaml và .env.example; không đụng .env thật.</t>
@@ -1556,49 +1522,15 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="36">
-      <c r="A18" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>ND2</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Tuần 5</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>Tra giá thật A1/A2/A3 trên dashboard gateway, điền cost_budget.md §3 và §5, đặt hard cap và cảnh báo ở mức 80% hạn mức</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>docs/cost_budget.md (§3, §5)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>11/10/2026</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Bắt buộc trước khi chạy bất kỳ lô nào. Không mở/sửa .env thay người dùng</t>
-        </is>
-      </c>
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="23" t="n"/>
       <c r="J18" s="26" t="inlineStr">
         <is>
           <t>Claude dựng bảng tính chi phí theo công thức; TA tra đơn giá thật trên dashboard.</t>
@@ -1678,45 +1610,45 @@
       <c r="J20" s="34" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="36">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>ND3</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Tuần 6</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Thiết kế kiến trúc testbed 5 tầng: lõi agent · tầng công cụ MCP · kho tri thức · tầng phòng thủ · tầng đo lường; định nghĩa điểm móc (hook) để cắm phòng thủ</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>Hình kiến trúc + đặc tả interface</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>12/10/2026</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>18/10/2026</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>config/ là hợp đồng, viết trước src/</t>
         </is>
@@ -1771,7 +1703,7 @@
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>ĐÃ KHOÁ bằng tag v-bench-1.0 — QUY TẮC CỨNG #1: không sửa</t>
+          <t>QUY TẮC CỨNG #1: không sửa/khóa theo quy tắc cứng #1</t>
         </is>
       </c>
       <c r="J22" s="26" t="inlineStr">
@@ -1870,12 +1802,16 @@
           <t>25/10/2026</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="n"/>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>Xong (đặc tả)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>Đặc tả T1–T8 + D1–D4 xong (payload_taxonomy.md, defense_spec.md). Phần code: validator schema.py + 17 payload mẫu (đủ 8 kỹ thuật) + worksheet + hướng dẫn, validate 20 test xanh. CÒN: GVHD rà câu chữ payload; tập payload đầy đủ + pilot defense=OFF (chặn bởi lõi agent STT-26) + gán nhãn kép κ≥0,80 + khóa v-attack-1.0.</t>
+        </is>
+      </c>
       <c r="J24" s="26" t="inlineStr">
         <is>
           <t>Claude viết đặc tả T1–T8, D1–D4 theo một mẫu thống nhất; TA chốt ranh giới để không trùng.</t>
